--- a/lead_generation_forms/010_warehouse_sponsorship_inquiry--lead_generation_forms.xlsx
+++ b/lead_generation_forms/010_warehouse_sponsorship_inquiry--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'lead_generation_forms'}</t>
+          <t>lead_generation_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Lead Generation Forms'}</t>
+          <t>Lead Generation Forms</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'landline'}</t>
+          <t>landline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Landline'}</t>
+          <t>Landline</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'australia'}</t>
+          <t>australia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Australia'}</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'nsw'}</t>
+          <t>nsw</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'NSW'}</t>
+          <t>NSW</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'vic'}</t>
+          <t>vic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'VIC'}</t>
+          <t>VIC</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'qld'}</t>
+          <t>qld</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'QLD'}</t>
+          <t>QLD</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'sa'}</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'SA'}</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'act'}</t>
+          <t>act</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'ACT'}</t>
+          <t>ACT</t>
         </is>
       </c>
     </row>
